--- a/application list.xlsx
+++ b/application list.xlsx
@@ -53693,7 +53693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M57"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -54107,12 +54107,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Business School</t>
+          <t>BAY AREA INTERNATIONAL BUSINESS SCHOOL</t>
         </is>
       </c>
       <c r="H10" s="13" t="inlineStr">
         <is>
-          <t>Business School</t>
+          <t>BAY AREA INTERNATIONAL BUSINESS SCHOOL</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -54122,7 +54122,7 @@
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=96DC1B7F3204BD16</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=4AC7F281ECBD2BA4</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -54139,17 +54139,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Beijing Normal University</t>
+          <t>Capital University of Economics and Business</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>BAY AREA INTERNATIONAL BUSINESS SCHOOL</t>
+          <t>International School of Economics and Management</t>
         </is>
       </c>
       <c r="H11" s="13" t="inlineStr">
         <is>
-          <t>BAY AREA INTERNATIONAL BUSINESS SCHOOL</t>
+          <t>International School of Economics and Management</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -54159,7 +54159,7 @@
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=4AC7F281ECBD2BA4</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=230A8F8CAE8FB702</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -54176,17 +54176,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Capital University of Economics and Business</t>
+          <t>Dongbei University of Finance &amp; Economics</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>International School of Economics and Management</t>
+          <t>Institute for Advanced Economic Research</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="H12" s="13" t="inlineStr">
         <is>
-          <t>International School of Economics and Management</t>
+          <t>Institute for Advanced Economic Research</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -54196,7 +54201,7 @@
       </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=230A8F8CAE8FB702</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=416DCA32DD657A3E</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -54213,22 +54218,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dongbei University of Finance &amp; Economics</t>
+          <t>Donghua University</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Institute for Advanced Economic Research</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2024-12-01</t>
+          <t>Glorious Sun School of Business and Management</t>
         </is>
       </c>
       <c r="H13" s="13" t="inlineStr">
         <is>
-          <t>Institute for Advanced Economic Research</t>
+          <t>Glorious Sun School of Business and Management</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -54238,7 +54238,7 @@
       </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=416DCA32DD657A3E</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=1CE68DDB85B84365</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -54255,17 +54255,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Donghua University</t>
+          <t>East China Normal University</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Glorious Sun School of Business and Management</t>
+          <t>School of Economics and Management</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="H14" s="13" t="inlineStr">
         <is>
-          <t>Glorious Sun School of Business and Management</t>
+          <t>School of Economics and Management</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -54275,7 +54280,7 @@
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=1CE68DDB85B84365</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=02D0B642A4713897</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -54292,22 +54297,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>East China Normal University</t>
+          <t>Fudan University</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>School of Economics and Management</t>
+          <t>School of Economics</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="H15" s="13" t="inlineStr">
         <is>
-          <t>School of Economics and Management</t>
+          <t>School of Economics</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -54317,7 +54322,7 @@
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=02D0B642A4713897</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=E968D280DD59D564</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -54339,17 +54344,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>School of Economics</t>
+          <t>School of Management</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>Rolling</t>
         </is>
       </c>
       <c r="H16" s="13" t="inlineStr">
         <is>
-          <t>School of Economics</t>
+          <t>School of Management</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -54359,7 +54364,7 @@
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=E968D280DD59D564</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=E153FEE8CC8E11B5</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -54381,17 +54386,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>School of Management</t>
+          <t>International School of Finance</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rolling</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="H17" s="13" t="inlineStr">
         <is>
-          <t>School of Management</t>
+          <t>International School of Finance</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -54401,7 +54406,7 @@
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=E153FEE8CC8E11B5</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=1EB0900D191FE938</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -54418,22 +54423,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Fudan University</t>
+          <t>Harbin Institute of Technology</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>International School of Finance</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2024-12-01</t>
+          <t>School of Management</t>
         </is>
       </c>
       <c r="H18" s="13" t="inlineStr">
         <is>
-          <t>International School of Finance</t>
+          <t>School of Management</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -54443,7 +54443,7 @@
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=1EB0900D191FE938</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=3ED8A58471D2F80B</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -54460,17 +54460,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Harbin Institute of Technology</t>
+          <t>Huazhong University of Science and Technology</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>School of Management</t>
+          <t>School of Economics, Huazhong University of Science &amp; Technology</t>
         </is>
       </c>
       <c r="H19" s="13" t="inlineStr">
         <is>
-          <t>School of Management</t>
+          <t>School of Economics, Huazhong University of Science &amp; Technology</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>CV; Job Market Paper; Letters of Reference</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -54480,7 +54485,7 @@
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=3ED8A58471D2F80B</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=A380FA8882023C78</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -54497,22 +54502,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Huazhong University of Science and Technology</t>
+          <t>Hunan University</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>School of Economics, Huazhong University of Science &amp; Technology</t>
+          <t>School of Economics and Trade</t>
         </is>
       </c>
       <c r="H20" s="13" t="inlineStr">
         <is>
-          <t>School of Economics, Huazhong University of Science &amp; Technology</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>CV; Job Market Paper; Letters of Reference</t>
+          <t>School of Economics and Trade</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -54522,7 +54522,7 @@
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=A380FA8882023C78</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=38CE3CA2770AB83B</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -54539,17 +54539,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Hunan University</t>
+          <t>Jinan University</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>School of Economics and Trade</t>
+          <t>School of Economics(SOE)</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2023-11-30</t>
         </is>
       </c>
       <c r="H21" s="13" t="inlineStr">
         <is>
-          <t>School of Economics and Trade</t>
+          <t>School of Economics(SOE)</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -54559,7 +54564,7 @@
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=38CE3CA2770AB83B</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=071E9B3AC5A0F760</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -54576,22 +54581,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jinan University</t>
+          <t>Lanzhou University of Finance and Economics</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>School of Economics(SOE)</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2023-11-30</t>
+          <t>the Office of Personnel</t>
         </is>
       </c>
       <c r="H22" s="13" t="inlineStr">
         <is>
-          <t>School of Economics(SOE)</t>
+          <t>the Office of Personnel</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -54601,7 +54601,7 @@
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=071E9B3AC5A0F760</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=003923B6EFE42FFF</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -54618,17 +54618,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Lanzhou University of Finance and Economics</t>
+          <t>Nanjing Agricultural University</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>the Office of Personnel</t>
+          <t>College of Finance</t>
         </is>
       </c>
       <c r="H23" s="13" t="inlineStr">
         <is>
-          <t>the Office of Personnel</t>
+          <t>College of Finance</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -54638,7 +54638,7 @@
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=003923B6EFE42FFF</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=41CE1E8D1AE20F34</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -54655,17 +54655,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Nanjing Agricultural University</t>
+          <t>Nanjing University</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>College of Finance</t>
+          <t>Business School</t>
         </is>
       </c>
       <c r="H24" s="13" t="inlineStr">
         <is>
-          <t>College of Finance</t>
+          <t>Business School</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -54675,7 +54675,7 @@
       </c>
       <c r="K24" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=41CE1E8D1AE20F34</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=5EE87D5DE6734D4D</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -54692,17 +54692,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Nanjing University</t>
+          <t>Nankai University</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Business School</t>
+          <t>School of Economics</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="H25" s="13" t="inlineStr">
         <is>
-          <t>Business School</t>
+          <t>School of Economics</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -54712,7 +54717,7 @@
       </c>
       <c r="K25" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=5EE87D5DE6734D4D</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=FDC08442010B7BC2</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -54734,17 +54739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>School of Economics</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2025-12-07</t>
+          <t>School of Finance</t>
         </is>
       </c>
       <c r="H26" s="13" t="inlineStr">
         <is>
-          <t>School of Economics</t>
+          <t>School of Finance</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -54754,7 +54754,7 @@
       </c>
       <c r="K26" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=FDC08442010B7BC2</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=96728BEC2B0A48B6</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -54771,17 +54771,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Nankai University</t>
+          <t>Peking University</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>School of Finance</t>
+          <t>Guanghua School of Management</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Rolling</t>
         </is>
       </c>
       <c r="H27" s="13" t="inlineStr">
         <is>
-          <t>School of Finance</t>
+          <t>Guanghua School of Management</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -54791,7 +54796,7 @@
       </c>
       <c r="K27" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=96728BEC2B0A48B6</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=B2D1A3FBC0575542</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -54813,17 +54818,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Guanghua School of Management</t>
+          <t>Peking University HSBC Business School</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rolling</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="H28" s="13" t="inlineStr">
         <is>
-          <t>Guanghua School of Management</t>
+          <t>Peking University HSBC Business School</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -54833,7 +54838,7 @@
       </c>
       <c r="K28" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=B2D1A3FBC0575542</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=6AA44C52147BF1AA</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -54850,22 +54855,27 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Peking University</t>
+          <t>Renmin University of China</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Peking University HSBC Business School</t>
+          <t>School of Economics</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="H29" s="13" t="inlineStr">
         <is>
-          <t>Peking University HSBC Business School</t>
+          <t>School of Economics</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>CV; Job Market Paper; Letters of Reference</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -54875,7 +54885,7 @@
       </c>
       <c r="K29" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=6AA44C52147BF1AA</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=D7AB329AF0E6B516</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -54892,17 +54902,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remin University</t>
+          <t>Renmin University of China</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>School of Applied Economics</t>
+          <t>School of Finance, Renmin University of China</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="H30" s="13" t="inlineStr">
         <is>
-          <t>School of Applied Economics</t>
+          <t>School of Finance, Renmin University of China</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -54912,7 +54927,7 @@
       </c>
       <c r="K30" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=680004BD3C688FB5</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=A2C98A6CF51DA6B8</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -54929,27 +54944,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Renmin University of China</t>
+          <t>Shanghai Institute for Mathematics and Interdisciplinary Sciences</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>School of Economics</t>
+          <t>The Shanghai Institute for Mathematics and Interdisciplinary Sciences</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="H31" s="13" t="inlineStr">
         <is>
-          <t>School of Economics</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>CV; Job Market Paper; Letters of Reference</t>
+          <t>The Shanghai Institute for Mathematics and Interdisciplinary Sciences</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -54959,7 +54969,7 @@
       </c>
       <c r="K31" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=D7AB329AF0E6B516</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=D6296C379B46AFF9</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -54976,22 +54986,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Renmin University of China</t>
+          <t>Shanghai Jiao Tong University</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>School of Finance, Renmin University of China</t>
+          <t>Antai College of Economics and Management</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="H32" s="13" t="inlineStr">
         <is>
-          <t>School of Finance, Renmin University of China</t>
+          <t>Antai College of Economics and Management</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -55001,7 +55011,7 @@
       </c>
       <c r="K32" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=A2C98A6CF51DA6B8</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=A718B6651C5FE241</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -55018,22 +55028,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Shanghai Institute for Mathematics and Interdisciplinary Sciences</t>
+          <t>Shanghai University of Finance and Economics</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>The Shanghai Institute for Mathematics and Interdisciplinary Sciences</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2025-03-31</t>
+          <t>School of Economics</t>
         </is>
       </c>
       <c r="H33" s="13" t="inlineStr">
         <is>
-          <t>The Shanghai Institute for Mathematics and Interdisciplinary Sciences</t>
+          <t>School of Economics</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -55043,7 +55048,7 @@
       </c>
       <c r="K33" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=D6296C379B46AFF9</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=3E6981392FF08E75</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -55060,22 +55065,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Shanghai Jiao Tong University</t>
+          <t>Shanghai University of Finance Economics School</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Antai College of Economics and Management</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-11-15</t>
+          <t>School of Digital Economy</t>
         </is>
       </c>
       <c r="H34" s="13" t="inlineStr">
         <is>
-          <t>Antai College of Economics and Management</t>
+          <t>School of Digital Economy</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -55085,7 +55085,7 @@
       </c>
       <c r="K34" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=A718B6651C5FE241</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=7E509CEAE1E65959</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -55102,17 +55102,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Shanghai University of Finance and Economics</t>
+          <t>Sichuan University</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>School of Economics</t>
+          <t>The School of Economics of Sichuan University</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="H35" s="13" t="inlineStr">
         <is>
-          <t>School of Economics</t>
+          <t>The School of Economics of Sichuan University</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -55122,7 +55127,7 @@
       </c>
       <c r="K35" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=3E6981392FF08E75</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=4D01E5935B5738A3</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -55139,17 +55144,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Shanghai University of Finance Economics School</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>School of Digital Economy</t>
+          <t>Southern University of Science and Technology</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2023-12-10</t>
         </is>
       </c>
       <c r="H36" s="13" t="inlineStr">
         <is>
-          <t>School of Digital Economy</t>
+          <t>Southern University of Science and Technology</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -55159,7 +55164,7 @@
       </c>
       <c r="K36" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=7E509CEAE1E65959</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=3EF86BA9413BD79E</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -55176,17 +55181,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Shanghai University of Finance and Economics</t>
+          <t>Southwestern University of Finance and Economics</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Dishui Lake Advanced Finance Institute</t>
+          <t>School of Economics</t>
         </is>
       </c>
       <c r="H37" s="13" t="inlineStr">
         <is>
-          <t>Dishui Lake Advanced Finance Institute</t>
+          <t>School of Economics</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -55196,7 +55201,7 @@
       </c>
       <c r="K37" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=5D5B5B1874A95B18</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=8F2A4E7B41A62BEC</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -55213,22 +55218,27 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sichuan University</t>
+          <t>Southwestern University of Finance&amp;;Economics</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>The School of Economics of Sichuan University</t>
+          <t>Research Institute of Economics and Management</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2023-12-01</t>
         </is>
       </c>
       <c r="H38" s="13" t="inlineStr">
         <is>
-          <t>The School of Economics of Sichuan University</t>
+          <t>Research Institute of Economics and Management</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>CV; Job Market Paper; Letters of Reference</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -55238,7 +55248,7 @@
       </c>
       <c r="K38" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=4D01E5935B5738A3</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=DB9471D924F0FD44</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -55255,17 +55265,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Southern University of Science and Technology</t>
+          <t>Sun Yat-sen University</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Lingnan College</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2023-12-10</t>
+          <t>2023-05-12</t>
         </is>
       </c>
       <c r="H39" s="13" t="inlineStr">
         <is>
-          <t>Southern University of Science and Technology</t>
+          <t>Lingnan College</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -55275,7 +55290,7 @@
       </c>
       <c r="K39" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=3EF86BA9413BD79E</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=73CF283104D9C7BB</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -55292,17 +55307,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Southwestern University of Finance and Economics</t>
+          <t>The Chinese University of Hong Kong</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>School of Economics</t>
+          <t>Department of Economics</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
         </is>
       </c>
       <c r="H40" s="13" t="inlineStr">
         <is>
-          <t>School of Economics</t>
+          <t>Department of Economics</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -55312,7 +55332,7 @@
       </c>
       <c r="K40" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=8F2A4E7B41A62BEC</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=0204A4EECEEA66C1</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -55329,27 +55349,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Southwestern University of Finance&amp;;Economics</t>
+          <t>Tianjin University</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Research Institute of Economics and Management</t>
+          <t>Ma Yinchu School of Economics</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2023-12-01</t>
+          <t>2023-11-15</t>
         </is>
       </c>
       <c r="H41" s="13" t="inlineStr">
         <is>
-          <t>Research Institute of Economics and Management</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>CV; Job Market Paper; Letters of Reference</t>
+          <t>Ma Yinchu School of Economics</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -55359,7 +55374,7 @@
       </c>
       <c r="K41" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=DB9471D924F0FD44</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=3514AA8724F3F9F8</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -55376,22 +55391,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sun Yat-sen University</t>
+          <t>Tsinghua University</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Lingnan College</t>
+          <t>School of Economics and Management</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2023-05-12</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="H42" s="13" t="inlineStr">
         <is>
-          <t>Lingnan College</t>
+          <t>School of Economics and Management</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -55401,7 +55416,7 @@
       </c>
       <c r="K42" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=73CF283104D9C7BB</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=EB34146E1220A115</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -55418,22 +55433,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>The Chinese University of Hong Kong</t>
+          <t>Tsinghua University</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Department of Economics</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2024-11-30</t>
+          <t>Center for International Finance and Economics Research</t>
         </is>
       </c>
       <c r="H43" s="13" t="inlineStr">
         <is>
-          <t>Department of Economics</t>
+          <t>Center for International Finance and Economics Research</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -55443,7 +55453,7 @@
       </c>
       <c r="K43" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=0204A4EECEEA66C1</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=6A1E66715A3A82D9</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -55460,22 +55470,17 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Tianjin University</t>
+          <t>University of Electronic Science and Technology of China</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ma Yinchu School of Economics</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2023-11-15</t>
+          <t>School of Management and Economics</t>
         </is>
       </c>
       <c r="H44" s="13" t="inlineStr">
         <is>
-          <t>Ma Yinchu School of Economics</t>
+          <t>School of Management and Economics</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -55485,7 +55490,7 @@
       </c>
       <c r="K44" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=3514AA8724F3F9F8</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=390B333672086D05</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -55502,17 +55507,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tongji University</t>
+          <t>University of Science and Technology of China</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>nothing</t>
+          <t>School of Management</t>
         </is>
       </c>
       <c r="H45" s="13" t="inlineStr">
         <is>
-          <t>nothing</t>
+          <t>School of Management</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -55522,7 +55527,7 @@
       </c>
       <c r="K45" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=41EFAE6DC817CCD8</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=6CAF00207D46BD36</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -55539,17 +55544,17 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Tsinghua University</t>
+          <t>University of Science and Technology of China</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>School of Social Sciences</t>
+          <t>Institute of International Finance</t>
         </is>
       </c>
       <c r="H46" s="13" t="inlineStr">
         <is>
-          <t>School of Social Sciences</t>
+          <t>Institute of International Finance</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -55559,7 +55564,7 @@
       </c>
       <c r="K46" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=48673CE5E9319FD6</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=612A2FEECB1FB3D7</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -55576,7 +55581,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tsinghua University</t>
+          <t>Wuhan University</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -55586,7 +55591,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2023-11-30</t>
         </is>
       </c>
       <c r="H47" s="13" t="inlineStr">
@@ -55601,7 +55606,7 @@
       </c>
       <c r="K47" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=EB34146E1220A115</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=A2DDB669D0484F72</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -55618,17 +55623,17 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Tsinghua University</t>
+          <t>Xi%u2019an Jiaotong University</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Center for International Finance and Economics Research</t>
+          <t>School of Economics and Finance</t>
         </is>
       </c>
       <c r="H48" s="13" t="inlineStr">
         <is>
-          <t>Center for International Finance and Economics Research</t>
+          <t>School of Economics and Finance</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -55638,7 +55643,7 @@
       </c>
       <c r="K48" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=6A1E66715A3A82D9</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=C3A72C51D391769E</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -55655,17 +55660,17 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>University of Electronic Science and Technology of China</t>
+          <t>Xi%u2019an Jiaotong-Liverpool University</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>School of Management and Economics</t>
+          <t>International Business School Suzhou (IBSS), Department of Economics</t>
         </is>
       </c>
       <c r="H49" s="13" t="inlineStr">
         <is>
-          <t>School of Management and Economics</t>
+          <t>International Business School Suzhou (IBSS), Department of Economics</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -55675,7 +55680,7 @@
       </c>
       <c r="K49" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=390B333672086D05</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=038CBF83FD61166B</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -55692,17 +55697,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>University of Science and Technology of China</t>
+          <t>Zhejiang University</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>School of Management</t>
+          <t>School of Economics</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="H50" s="13" t="inlineStr">
         <is>
-          <t>School of Management</t>
+          <t>School of Economics</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -55712,7 +55722,7 @@
       </c>
       <c r="K50" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=6CAF00207D46BD36</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=7D928B7B1C35099A</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -55729,17 +55739,17 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>University of Science and Technology of China</t>
+          <t>Zhejiang University</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Institute of International Finance</t>
+          <t>International Business School</t>
         </is>
       </c>
       <c r="H51" s="13" t="inlineStr">
         <is>
-          <t>Institute of International Finance</t>
+          <t>International Business School</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -55749,7 +55759,7 @@
       </c>
       <c r="K51" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=612A2FEECB1FB3D7</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=AB6EF80CCC4E40B3</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -55766,22 +55776,17 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Wuhan University</t>
+          <t>Zhongnan Unviersity of Economics and Law</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>School of Economics and Management</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2023-11-30</t>
+          <t>School of Finance</t>
         </is>
       </c>
       <c r="H52" s="13" t="inlineStr">
         <is>
-          <t>School of Economics and Management</t>
+          <t>School of Finance</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -55791,200 +55796,10 @@
       </c>
       <c r="K52" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=A2DDB669D0484F72</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=2FC3B168FE2DBD23</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
-        <is>
-          <t>Faculty</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Xi%u2019an Jiaotong University</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>School of Economics and Finance</t>
-        </is>
-      </c>
-      <c r="H53" s="13" t="inlineStr">
-        <is>
-          <t>School of Economics and Finance</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>CICE</t>
-        </is>
-      </c>
-      <c r="K53" s="13" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=C3A72C51D391769E</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>Faculty</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Xi%u2019an Jiaotong-Liverpool University</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>International Business School Suzhou (IBSS), Department of Economics</t>
-        </is>
-      </c>
-      <c r="H54" s="13" t="inlineStr">
-        <is>
-          <t>International Business School Suzhou (IBSS), Department of Economics</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>CICE</t>
-        </is>
-      </c>
-      <c r="K54" s="13" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=038CBF83FD61166B</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>Faculty</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Zhejiang University</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>School of Economics</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="H55" s="13" t="inlineStr">
-        <is>
-          <t>School of Economics</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>CICE</t>
-        </is>
-      </c>
-      <c r="K55" s="13" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=7D928B7B1C35099A</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>Faculty</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Zhejiang University</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>International Business School</t>
-        </is>
-      </c>
-      <c r="H56" s="13" t="inlineStr">
-        <is>
-          <t>International Business School</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>CICE</t>
-        </is>
-      </c>
-      <c r="K56" s="13" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=AB6EF80CCC4E40B3</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>Faculty</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Zhongnan Unviersity of Economics and Law</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>School of Finance</t>
-        </is>
-      </c>
-      <c r="H57" s="13" t="inlineStr">
-        <is>
-          <t>School of Finance</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>CICE</t>
-        </is>
-      </c>
-      <c r="K57" s="13" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=2FC3B168FE2DBD23</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
         <is>
           <t>Faculty</t>
         </is>
@@ -56094,16 +55909,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K51" r:id="rId100"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H52" r:id="rId101"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K52" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H53" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K53" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H54" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K54" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K55" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H56" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K56" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H57" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K57" r:id="rId112"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/application list.xlsx
+++ b/application list.xlsx
@@ -13538,7 +13538,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2027-02-28</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H3" s="13" t="inlineStr">
@@ -13719,6 +13719,11 @@
           <t>Economics</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-11-01</t>
+        </is>
+      </c>
       <c r="H7" s="13" t="inlineStr">
         <is>
           <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111478043</t>
@@ -13766,6 +13771,11 @@
           <t>Economics</t>
         </is>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-11-01</t>
+        </is>
+      </c>
       <c r="H8" s="13" t="inlineStr">
         <is>
           <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111478044</t>
@@ -13872,7 +13882,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="H10" s="13" t="inlineStr">
@@ -14080,7 +14090,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2027-04-30</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="H14" s="13" t="inlineStr">
@@ -14585,7 +14595,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2027-02-15</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="H24" s="13" t="inlineStr">
@@ -14632,7 +14642,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="H25" s="13" t="inlineStr">
@@ -14773,7 +14783,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="H28" s="13" t="inlineStr">
@@ -14815,7 +14825,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="H29" s="13" t="inlineStr">
@@ -14872,7 +14882,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H30" s="13" t="inlineStr">
@@ -14919,7 +14929,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2027-03-01</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="H31" s="13" t="inlineStr">
@@ -14971,7 +14981,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2027-03-01</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H32" s="13" t="inlineStr">
@@ -15023,7 +15033,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2027-03-01</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H33" s="13" t="inlineStr">
@@ -15075,7 +15085,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2027-07-01</t>
         </is>
       </c>
       <c r="H34" s="13" t="inlineStr">
@@ -15283,7 +15293,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>Rolling</t>
         </is>
       </c>
       <c r="H38" s="13" t="inlineStr">
@@ -15419,7 +15429,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2027-03-01</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="H41" s="13" t="inlineStr">
@@ -15763,7 +15773,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="H48" s="13" t="inlineStr">
@@ -16251,6 +16261,11 @@
           <t>Economics</t>
         </is>
       </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-11-15</t>
+        </is>
+      </c>
       <c r="H58" s="13" t="inlineStr">
         <is>
           <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477940</t>
@@ -16298,6 +16313,11 @@
           <t>Economics</t>
         </is>
       </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-11-15</t>
+        </is>
+      </c>
       <c r="H59" s="13" t="inlineStr">
         <is>
           <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477942</t>
@@ -16446,7 +16466,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H62" s="13" t="inlineStr">
@@ -16488,7 +16508,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H63" s="13" t="inlineStr">
@@ -17060,7 +17080,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H74" s="13" t="inlineStr">
@@ -17498,7 +17518,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H83" s="13" t="inlineStr">
@@ -17822,7 +17842,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="H90" s="13" t="inlineStr">
@@ -17869,7 +17889,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="H91" s="13" t="inlineStr">
@@ -17916,7 +17936,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="H92" s="13" t="inlineStr">
@@ -18005,7 +18025,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2027-08-31</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H94" s="13" t="inlineStr">
@@ -18619,7 +18639,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2027-01-01</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="H106" s="13" t="inlineStr">
@@ -18901,7 +18921,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H112" s="13" t="inlineStr">
@@ -19228,7 +19248,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="H118" s="13" t="inlineStr">
@@ -19280,7 +19300,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="H119" s="13" t="inlineStr">
@@ -19718,7 +19738,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2027-09-18</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H128" s="13" t="inlineStr">
@@ -19921,7 +19941,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="H132" s="13" t="inlineStr">
@@ -19978,7 +19998,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H133" s="13" t="inlineStr">
@@ -20080,6 +20100,11 @@
           <t>Economics</t>
         </is>
       </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-11-15</t>
+        </is>
+      </c>
       <c r="H135" s="13" t="inlineStr">
         <is>
           <t>Listing</t>
@@ -20134,7 +20159,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H136" s="13" t="inlineStr">
@@ -20357,7 +20382,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H140" s="13" t="inlineStr">
@@ -20748,7 +20773,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H148" s="13" t="inlineStr">
@@ -21941,7 +21966,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="H172" s="13" t="inlineStr">
@@ -22713,7 +22738,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="H188" s="13" t="inlineStr">
@@ -22906,7 +22931,7 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H192" s="13" t="inlineStr">
@@ -23094,7 +23119,7 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>2027-02-20</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H196" s="13" t="inlineStr">
@@ -23535,6 +23560,11 @@
           <t>Economics</t>
         </is>
       </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>2026-11-20</t>
+        </is>
+      </c>
       <c r="H205" s="13" t="inlineStr">
         <is>
           <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477934</t>
@@ -23584,7 +23614,7 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="H206" s="13" t="inlineStr">
@@ -23683,7 +23713,7 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>2027-02-27</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H208" s="13" t="inlineStr">
@@ -23725,7 +23755,7 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>2027-02-27</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H209" s="13" t="inlineStr">
@@ -23819,7 +23849,7 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>2027-04-30</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="H211" s="13" t="inlineStr">
@@ -24393,7 +24423,7 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>Rolling</t>
         </is>
       </c>
       <c r="H223" s="13" t="inlineStr">
@@ -25943,7 +25973,7 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2027-09-30</t>
         </is>
       </c>
       <c r="H253" s="13" t="inlineStr">
@@ -26097,6 +26127,11 @@
           <t>Economics</t>
         </is>
       </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>2026-11-01</t>
+        </is>
+      </c>
       <c r="H256" s="13" t="inlineStr">
         <is>
           <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477860</t>
@@ -26146,7 +26181,7 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>2027-08-06</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H257" s="13" t="inlineStr">
@@ -26245,7 +26280,7 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="H259" s="13" t="inlineStr">
@@ -26302,7 +26337,7 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="H260" s="13" t="inlineStr">
@@ -26453,7 +26488,7 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="H263" s="13" t="inlineStr">
@@ -26671,7 +26706,7 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H267" s="13" t="inlineStr">
@@ -26827,7 +26862,7 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H270" s="13" t="inlineStr">
@@ -27129,7 +27164,7 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H276" s="13" t="inlineStr">
@@ -27228,7 +27263,7 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="H278" s="13" t="inlineStr">
@@ -27894,7 +27929,7 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>2027-07-01</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H291" s="13" t="inlineStr">
@@ -28030,7 +28065,7 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>2027-04-01</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H294" s="13" t="inlineStr">
@@ -28181,7 +28216,7 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="H297" s="13" t="inlineStr">
@@ -28238,7 +28273,7 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>2027-02-28</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="H298" s="13" t="inlineStr">
@@ -28486,6 +28521,11 @@
           <t>Resources for the Future</t>
         </is>
       </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>2027-01-31</t>
+        </is>
+      </c>
       <c r="H303" s="13" t="inlineStr">
         <is>
           <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477485</t>
@@ -28686,7 +28726,7 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>Rolling</t>
         </is>
       </c>
       <c r="H307" s="13" t="inlineStr">
@@ -29644,7 +29684,7 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2027-01-04</t>
         </is>
       </c>
       <c r="H326" s="13" t="inlineStr">
@@ -30003,7 +30043,7 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="H333" s="13" t="inlineStr">
@@ -31087,7 +31127,7 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H355" s="13" t="inlineStr">
@@ -31451,7 +31491,7 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>2027-03-20</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H362" s="13" t="inlineStr">
@@ -32094,7 +32134,7 @@
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H376" s="13" t="inlineStr">
@@ -32451,6 +32491,11 @@
           <t>Kenneth C. Griffin Department of Economics</t>
         </is>
       </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="H383" s="13" t="inlineStr">
         <is>
           <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477913</t>
@@ -32505,7 +32550,7 @@
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>2027-06-30</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H384" s="13" t="inlineStr">
@@ -32562,7 +32607,7 @@
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>2027-06-30</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H385" s="13" t="inlineStr">
@@ -32614,7 +32659,7 @@
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="H386" s="13" t="inlineStr">
@@ -32916,7 +32961,7 @@
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H392" s="13" t="inlineStr">
@@ -32963,7 +33008,7 @@
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>Rolling</t>
         </is>
       </c>
       <c r="H393" s="13" t="inlineStr">
@@ -33151,7 +33196,7 @@
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>2027-12-31</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H397" s="13" t="inlineStr">
@@ -33193,7 +33238,7 @@
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>2027-12-31</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H398" s="13" t="inlineStr">
@@ -33282,7 +33327,7 @@
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="H400" s="13" t="inlineStr">
@@ -33334,7 +33379,7 @@
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>2027-06-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="H401" s="13" t="inlineStr">
@@ -33438,7 +33483,7 @@
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H403" s="13" t="inlineStr">
@@ -33644,6 +33689,11 @@
           <t>University at Buffalo</t>
         </is>
       </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
       <c r="H407" s="13" t="inlineStr">
         <is>
           <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111478050</t>
@@ -33681,6 +33731,11 @@
           <t>University at Buffalo</t>
         </is>
       </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>2027-01-07</t>
+        </is>
+      </c>
       <c r="H408" s="13" t="inlineStr">
         <is>
           <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477851</t>
@@ -33876,7 +33931,7 @@
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H412" s="13" t="inlineStr">
@@ -34163,7 +34218,7 @@
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H418" s="13" t="inlineStr">
@@ -34210,7 +34265,7 @@
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H419" s="13" t="inlineStr">
@@ -34309,7 +34364,7 @@
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H421" s="13" t="inlineStr">
@@ -34403,7 +34458,7 @@
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>2027-08-30</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="H423" s="13" t="inlineStr">
@@ -34883,7 +34938,7 @@
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>2027-05-01</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H433" s="13" t="inlineStr">
@@ -34935,7 +34990,7 @@
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>2027-06-30</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H434" s="13" t="inlineStr">
@@ -34987,7 +35042,7 @@
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>2027-03-31</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H435" s="13" t="inlineStr">
@@ -35039,7 +35094,7 @@
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>2027-06-30</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H436" s="13" t="inlineStr">
@@ -35289,7 +35344,7 @@
       </c>
       <c r="F441" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2027-01-01</t>
         </is>
       </c>
       <c r="H441" s="13" t="inlineStr">
@@ -35388,7 +35443,7 @@
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2027-01-01</t>
         </is>
       </c>
       <c r="H443" s="13" t="inlineStr">
@@ -35492,7 +35547,7 @@
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H445" s="13" t="inlineStr">
@@ -35596,7 +35651,7 @@
       </c>
       <c r="F447" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="H447" s="13" t="inlineStr">
@@ -35653,7 +35708,7 @@
       </c>
       <c r="F448" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="H448" s="13" t="inlineStr">
@@ -35814,7 +35869,7 @@
       </c>
       <c r="F451" t="inlineStr">
         <is>
-          <t>2027-04-30</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H451" s="13" t="inlineStr">
@@ -36067,6 +36122,11 @@
           <t>Department of Finance and Business Economics</t>
         </is>
       </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
       <c r="H456" s="13" t="inlineStr">
         <is>
           <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477678</t>
@@ -36168,7 +36228,7 @@
       </c>
       <c r="F458" t="inlineStr">
         <is>
-          <t>2027-02-06</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H458" s="13" t="inlineStr">
@@ -36225,7 +36285,7 @@
       </c>
       <c r="F459" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="H459" s="13" t="inlineStr">
@@ -36324,7 +36384,7 @@
       </c>
       <c r="F461" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="H461" s="13" t="inlineStr">
@@ -36371,7 +36431,7 @@
       </c>
       <c r="F462" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H462" s="13" t="inlineStr">
@@ -36663,7 +36723,7 @@
       </c>
       <c r="F468" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H468" s="13" t="inlineStr">
@@ -36710,7 +36770,7 @@
       </c>
       <c r="F469" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H469" s="13" t="inlineStr">
@@ -36893,7 +36953,7 @@
       </c>
       <c r="F473" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H473" s="13" t="inlineStr">
@@ -36940,7 +37000,7 @@
       </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H474" s="13" t="inlineStr">
@@ -37519,7 +37579,7 @@
       </c>
       <c r="F486" t="inlineStr">
         <is>
-          <t>2027-04-07</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H486" s="13" t="inlineStr">
@@ -37774,7 +37834,7 @@
       </c>
       <c r="F491" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H491" s="13" t="inlineStr">
@@ -37821,7 +37881,7 @@
       </c>
       <c r="F492" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H492" s="13" t="inlineStr">
@@ -37868,7 +37928,7 @@
       </c>
       <c r="F493" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H493" s="13" t="inlineStr">
@@ -38086,7 +38146,7 @@
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>2027-05-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="H497" s="13" t="inlineStr">
@@ -38311,7 +38371,7 @@
       </c>
       <c r="F502" t="inlineStr">
         <is>
-          <t>2027-03-30</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H502" s="13" t="inlineStr">
@@ -38400,7 +38460,7 @@
       </c>
       <c r="F504" t="inlineStr">
         <is>
-          <t>2027-02-01</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H504" s="13" t="inlineStr">
@@ -38447,7 +38507,7 @@
       </c>
       <c r="F505" t="inlineStr">
         <is>
-          <t>2027-01-01</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="H505" s="13" t="inlineStr">
@@ -38494,7 +38554,7 @@
       </c>
       <c r="F506" t="inlineStr">
         <is>
-          <t>2027-01-01</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="H506" s="13" t="inlineStr">
@@ -38734,7 +38794,7 @@
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>2027-01-04</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="H511" s="13" t="inlineStr">
@@ -38907,7 +38967,7 @@
       </c>
       <c r="F515" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H515" s="13" t="inlineStr">
@@ -39120,7 +39180,7 @@
       </c>
       <c r="F519" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H519" s="13" t="inlineStr">
@@ -39167,7 +39227,7 @@
       </c>
       <c r="F520" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="H520" s="13" t="inlineStr">
@@ -39427,7 +39487,7 @@
       </c>
       <c r="F525" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="H525" s="13" t="inlineStr">
@@ -39781,7 +39841,7 @@
       </c>
       <c r="F532" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="H532" s="13" t="inlineStr">
@@ -41032,12 +41092,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-12-19</t>
         </is>
       </c>
       <c r="H2" s="13" t="inlineStr">
         <is>
-          <t>Pre-Doctoral Program – Global Talent Common Application</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -41084,12 +41144,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="H3" s="13" t="inlineStr">
         <is>
-          <t>Associate Professor/Professor in Quantitative Analysis of Markets and Organizati</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -41131,12 +41191,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="H4" s="13" t="inlineStr">
         <is>
-          <t>Junior Professor Chair (Tenure Track) in Public Policy Evaluation</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -41183,12 +41243,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H5" s="13" t="inlineStr">
         <is>
-          <t>PhD position in Economics: renewable energy auctions</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -41245,7 +41305,7 @@
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>Faculty Position in International Economics, Open Rank</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -41302,7 +41362,7 @@
       </c>
       <c r="H7" s="13" t="inlineStr">
         <is>
-          <t>S-Professorship for ‘International Economics’ (W3)</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -41359,7 +41419,7 @@
       </c>
       <c r="H8" s="13" t="inlineStr">
         <is>
-          <t>Tenured Associate or Full Professor of Economic Analysis</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -41411,7 +41471,7 @@
       </c>
       <c r="H9" s="13" t="inlineStr">
         <is>
-          <t>Dean, Faculty of Arts and Social Sciences, National University of Singapore</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -41463,7 +41523,7 @@
       </c>
       <c r="H10" s="13" t="inlineStr">
         <is>
-          <t>PhD scholarship in Sustainable Finance with Focus on Climate Banking</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -41520,7 +41580,7 @@
       </c>
       <c r="H11" s="13" t="inlineStr">
         <is>
-          <t>Assistant, Associate, or Full Professor of Health Policy (Health Economist)</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -41577,7 +41637,7 @@
       </c>
       <c r="H12" s="13" t="inlineStr">
         <is>
-          <t>Research Associate - Federal Reserve Bank of St. Louis</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -41602,7 +41662,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Postdoc</t>
+          <t>Faculty</t>
         </is>
       </c>
     </row>
@@ -41634,7 +41694,7 @@
       </c>
       <c r="H13" s="13" t="inlineStr">
         <is>
-          <t>Assistant Professor of Economics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -41691,7 +41751,7 @@
       </c>
       <c r="H14" s="13" t="inlineStr">
         <is>
-          <t>Faculty position in Arctic defence and security</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -41748,7 +41808,7 @@
       </c>
       <c r="H15" s="13" t="inlineStr">
         <is>
-          <t>Research Analyst</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -41800,7 +41860,7 @@
       </c>
       <c r="H16" s="13" t="inlineStr">
         <is>
-          <t>Monash Economics, Associate Professor</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -41857,7 +41917,7 @@
       </c>
       <c r="H17" s="13" t="inlineStr">
         <is>
-          <t>Associate Professor or DTU Tenure Track Assistant Professor</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -41914,7 +41974,7 @@
       </c>
       <c r="H18" s="13" t="inlineStr">
         <is>
-          <t>Assistant Professor (Tenure Track) in Macroeconomics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -41971,7 +42031,7 @@
       </c>
       <c r="H19" s="13" t="inlineStr">
         <is>
-          <t>Faculty Position in Global inequalities and trade</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -42028,7 +42088,7 @@
       </c>
       <c r="H20" s="13" t="inlineStr">
         <is>
-          <t>Faculty Position in Behavioral Economics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -42085,7 +42145,7 @@
       </c>
       <c r="H21" s="13" t="inlineStr">
         <is>
-          <t>Faculty Position in Applied Economics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -42142,7 +42202,7 @@
       </c>
       <c r="H22" s="13" t="inlineStr">
         <is>
-          <t>Faculty Position (Teaching Stream) in Economics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -42199,7 +42259,7 @@
       </c>
       <c r="H23" s="13" t="inlineStr">
         <is>
-          <t>Assistant and Associate level positions</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -42256,7 +42316,7 @@
       </c>
       <c r="H24" s="13" t="inlineStr">
         <is>
-          <t>Lecturer / Senior Lecturer in Economics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -42313,7 +42373,7 @@
       </c>
       <c r="H25" s="13" t="inlineStr">
         <is>
-          <t>PhD scholarships in Economics at the Department of Economics, University of Sout</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -42370,7 +42430,7 @@
       </c>
       <c r="H26" s="13" t="inlineStr">
         <is>
-          <t>Full Professor Banking &amp; Finance</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -42390,7 +42450,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -42422,7 +42482,7 @@
       </c>
       <c r="H27" s="13" t="inlineStr">
         <is>
-          <t>Faculty Positions in Finance</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -42479,7 +42539,7 @@
       </c>
       <c r="H28" s="13" t="inlineStr">
         <is>
-          <t>Assistant / Associate / Full Professors in Economics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -42536,7 +42596,7 @@
       </c>
       <c r="H29" s="13" t="inlineStr">
         <is>
-          <t>Assistant Professorship (tenure-track) in Economics of Sustainability</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -42593,7 +42653,7 @@
       </c>
       <c r="H30" s="13" t="inlineStr">
         <is>
-          <t>Tenure Track Assistant/Associate Professor, Institute of Economic Research</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -42650,7 +42710,7 @@
       </c>
       <c r="H31" s="13" t="inlineStr">
         <is>
-          <t>Assistant or Untenured Associate Professor – Tenure Track</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -42707,7 +42767,7 @@
       </c>
       <c r="H32" s="13" t="inlineStr">
         <is>
-          <t>Assistant Professor in Economics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -42764,7 +42824,7 @@
       </c>
       <c r="H33" s="13" t="inlineStr">
         <is>
-          <t>Assistant Professor in International Trade</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -42821,7 +42881,7 @@
       </c>
       <c r="H34" s="13" t="inlineStr">
         <is>
-          <t>Associate or Full Professor in Industrial Organization</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -42878,7 +42938,7 @@
       </c>
       <c r="H35" s="13" t="inlineStr">
         <is>
-          <t>Postdoctoral Position in Macroeconomics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -42935,7 +42995,7 @@
       </c>
       <c r="H36" s="13" t="inlineStr">
         <is>
-          <t>International Economic Policy (Assistant/Advanced Assistant Professor)</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -42992,7 +43052,7 @@
       </c>
       <c r="H37" s="13" t="inlineStr">
         <is>
-          <t>Assistant Professor -Tenure Track</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -43044,7 +43104,7 @@
       </c>
       <c r="H38" s="13" t="inlineStr">
         <is>
-          <t>Assistant Professor of Economics and Public Policy</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -43101,7 +43161,7 @@
       </c>
       <c r="H39" s="13" t="inlineStr">
         <is>
-          <t>Two Assistant professor positions in Sciences Po</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -43158,7 +43218,7 @@
       </c>
       <c r="H40" s="13" t="inlineStr">
         <is>
-          <t>Tenure Track Position in International Trade and/or Industrial Organization</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -43210,7 +43270,7 @@
       </c>
       <c r="H41" s="13" t="inlineStr">
         <is>
-          <t>Stanford Graduate School of Business - Faculty Positions in Economics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -43267,7 +43327,7 @@
       </c>
       <c r="H42" s="13" t="inlineStr">
         <is>
-          <t>Assistant Professor of Economics (Microeconomic Theory and/or Industrial Organiz</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -43324,7 +43384,7 @@
       </c>
       <c r="H43" s="13" t="inlineStr">
         <is>
-          <t>Assistant Professor of Economics (Applied Microeconomics)</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -43381,7 +43441,7 @@
       </c>
       <c r="H44" s="13" t="inlineStr">
         <is>
-          <t>Assistant Professor (Tenure-Track)</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -43438,7 +43498,7 @@
       </c>
       <c r="H45" s="13" t="inlineStr">
         <is>
-          <t>Assistant Professor of Economics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -43495,7 +43555,7 @@
       </c>
       <c r="H46" s="13" t="inlineStr">
         <is>
-          <t>Two Assistant Professor Positions in Economics for Junior Candidates</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -43542,7 +43602,7 @@
       </c>
       <c r="H47" s="13" t="inlineStr">
         <is>
-          <t>Assistant Professor positions</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -43594,7 +43654,7 @@
       </c>
       <c r="H48" s="13" t="inlineStr">
         <is>
-          <t>Assistant Professor (tenure track) in Finance or Accounting</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -43651,7 +43711,7 @@
       </c>
       <c r="H49" s="13" t="inlineStr">
         <is>
-          <t>Assistant Professor of International and Public Affairs</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -43708,7 +43768,7 @@
       </c>
       <c r="H50" s="13" t="inlineStr">
         <is>
-          <t>Assistant/Associate/Full Professor</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -43755,7 +43815,7 @@
       </c>
       <c r="H51" s="13" t="inlineStr">
         <is>
-          <t>Tenure-Track Assistant Professor in Finance 2027-2028</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -43807,7 +43867,7 @@
       </c>
       <c r="H52" s="13" t="inlineStr">
         <is>
-          <t>Tenure-Track Faculty Positions in Economics 2027-2028</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -43864,7 +43924,7 @@
       </c>
       <c r="H53" s="13" t="inlineStr">
         <is>
-          <t>Assistant Professor in Macroeconomics (tenure-track)</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -43911,7 +43971,7 @@
       </c>
       <c r="H54" s="13" t="inlineStr">
         <is>
-          <t>Assistant professor in Microeconomics and/or Public Economics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -43958,7 +44018,7 @@
       </c>
       <c r="H55" s="13" t="inlineStr">
         <is>
-          <t>Assistant Professor, Theory</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -44015,7 +44075,7 @@
       </c>
       <c r="H56" s="13" t="inlineStr">
         <is>
-          <t>Assistant Professor in Economics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -44067,7 +44127,7 @@
       </c>
       <c r="H57" s="13" t="inlineStr">
         <is>
-          <t>Assistant Professor in Managerial Economics and Decision Sciences</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -44124,7 +44184,7 @@
       </c>
       <c r="H58" s="13" t="inlineStr">
         <is>
-          <t>Assistant Professor in Strategy</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -44181,7 +44241,7 @@
       </c>
       <c r="H59" s="13" t="inlineStr">
         <is>
-          <t>Assistant Professor in Accounting Information &amp; Management</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -44238,7 +44298,7 @@
       </c>
       <c r="H60" s="13" t="inlineStr">
         <is>
-          <t>Associate of Full Professor in Economics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -44290,7 +44350,7 @@
       </c>
       <c r="H61" s="13" t="inlineStr">
         <is>
-          <t>Assistant Professor in Finance</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -44347,7 +44407,7 @@
       </c>
       <c r="H62" s="13" t="inlineStr">
         <is>
-          <t>Associate Professor in Accounting</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -44399,7 +44459,7 @@
       </c>
       <c r="H63" s="13" t="inlineStr">
         <is>
-          <t>Assistant Professor in Environmental Social Sciences</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -44456,7 +44516,7 @@
       </c>
       <c r="H64" s="13" t="inlineStr">
         <is>
-          <t>Assistant Professor in Labor Economics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -44513,7 +44573,7 @@
       </c>
       <c r="H65" s="13" t="inlineStr">
         <is>
-          <t>Tenure Track Position</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -44570,7 +44630,7 @@
       </c>
       <c r="H66" s="13" t="inlineStr">
         <is>
-          <t>Two Assistant Professorships in Econometrics (W1 with Tenure Track to W2)</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -44627,7 +44687,7 @@
       </c>
       <c r="H67" s="13" t="inlineStr">
         <is>
-          <t>Assistant Professor in Environmental Economics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -44684,7 +44744,7 @@
       </c>
       <c r="H68" s="13" t="inlineStr">
         <is>
-          <t>Assistant Professor in Applied Microeconomics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -44741,7 +44801,7 @@
       </c>
       <c r="H69" s="13" t="inlineStr">
         <is>
-          <t>Tenure-track Professor/Associate Professor/Assistant Professor (several posts)</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -44793,7 +44853,7 @@
       </c>
       <c r="H70" s="13" t="inlineStr">
         <is>
-          <t>Assistant Professor of Theoretical Public Economics (W1)</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -44845,7 +44905,7 @@
       </c>
       <c r="H71" s="13" t="inlineStr">
         <is>
-          <t>Two Assistant Professorships in Macroeconomics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -44897,7 +44957,7 @@
       </c>
       <c r="H72" s="13" t="inlineStr">
         <is>
-          <t>4329, ØI, PhD scholarships in Economics at the Department of Economics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -44954,7 +45014,7 @@
       </c>
       <c r="H73" s="13" t="inlineStr">
         <is>
-          <t>Assistant Professor of Economics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -45011,7 +45071,7 @@
       </c>
       <c r="H74" s="13" t="inlineStr">
         <is>
-          <t>Pre-Doctoral Program – Global Talent Common Application</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -45063,7 +45123,7 @@
       </c>
       <c r="H75" s="13" t="inlineStr">
         <is>
-          <t>Assistant Professor of Macroeconomics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -45120,7 +45180,7 @@
       </c>
       <c r="H76" s="13" t="inlineStr">
         <is>
-          <t>Assistant Professor of Applied Microeconomics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -45177,7 +45237,7 @@
       </c>
       <c r="H77" s="13" t="inlineStr">
         <is>
-          <t>Assistant, Advanced Assistant, Associate, or Full Professor of Economics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -45224,12 +45284,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="H78" s="13" t="inlineStr">
         <is>
-          <t>Faculty Positions at the Department of Finance, Copenhagen Business School</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -45281,7 +45341,7 @@
       </c>
       <c r="H79" s="13" t="inlineStr">
         <is>
-          <t>Assistant Professor of Economics (FGV EPGE - Rio)</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -45338,7 +45398,7 @@
       </c>
       <c r="H80" s="13" t="inlineStr">
         <is>
-          <t>Two tenure track positions in Economics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -45395,7 +45455,7 @@
       </c>
       <c r="H81" s="13" t="inlineStr">
         <is>
-          <t>Assistant Professor, Teaching Stream - Economics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -45452,7 +45512,7 @@
       </c>
       <c r="H82" s="13" t="inlineStr">
         <is>
-          <t>Assistant Professor, Environmental Economics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -45509,7 +45569,7 @@
       </c>
       <c r="H83" s="13" t="inlineStr">
         <is>
-          <t>Full-time academic Position in Policy-Relevant Applied Microeconomics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -45566,7 +45626,7 @@
       </c>
       <c r="H84" s="13" t="inlineStr">
         <is>
-          <t>Assistant Professor (tenure track) in Finance</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -45618,7 +45678,7 @@
       </c>
       <c r="H85" s="13" t="inlineStr">
         <is>
-          <t>Assistant, Associate or Full Professor of Economics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -45670,7 +45730,7 @@
       </c>
       <c r="H86" s="13" t="inlineStr">
         <is>
-          <t>Assistant Professor of Economics — Macroeconomics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -45727,7 +45787,7 @@
       </c>
       <c r="H87" s="13" t="inlineStr">
         <is>
-          <t>Assistant or Associate Professor in Finance</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -45779,7 +45839,7 @@
       </c>
       <c r="H88" s="13" t="inlineStr">
         <is>
-          <t>Assistant Professor - Finance - Haas School of Business</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -45836,7 +45896,7 @@
       </c>
       <c r="H89" s="13" t="inlineStr">
         <is>
-          <t>Assistant Professor - Economic Analysis &amp; Policy - Haas School of Business</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -45893,7 +45953,7 @@
       </c>
       <c r="H90" s="13" t="inlineStr">
         <is>
-          <t>Professor in international economics (any level)</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -45945,7 +46005,7 @@
       </c>
       <c r="H91" s="13" t="inlineStr">
         <is>
-          <t>Assistant/Associate Professor in Industrial Organization or Regulatory Economics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -46002,7 +46062,7 @@
       </c>
       <c r="H92" s="13" t="inlineStr">
         <is>
-          <t>Faculty positions in finance</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -46059,7 +46119,7 @@
       </c>
       <c r="H93" s="13" t="inlineStr">
         <is>
-          <t>Lecturer/Assistant Professor</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -46111,7 +46171,7 @@
       </c>
       <c r="H94" s="13" t="inlineStr">
         <is>
-          <t>Assistant Professorship in Finance (W1 with Tenure Track to W2)</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -46168,7 +46228,7 @@
       </c>
       <c r="H95" s="13" t="inlineStr">
         <is>
-          <t>Assistant Professor of Economics — Any field, Swedish speaking</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -46225,7 +46285,7 @@
       </c>
       <c r="H96" s="13" t="inlineStr">
         <is>
-          <t>Assistant Professor of Economics — Microeconomics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -46282,7 +46342,7 @@
       </c>
       <c r="H97" s="13" t="inlineStr">
         <is>
-          <t>Tenure-track Lecturer or Assistant Professor in Economics (two positions)</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -46339,7 +46399,7 @@
       </c>
       <c r="H98" s="13" t="inlineStr">
         <is>
-          <t>Two Assistant Professor Positions in Economics (any field) at ISEG - Lisbon</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -46396,7 +46456,7 @@
       </c>
       <c r="H99" s="13" t="inlineStr">
         <is>
-          <t>Senior Lecturer, Economics / Econometrics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -46453,7 +46513,7 @@
       </c>
       <c r="H100" s="13" t="inlineStr">
         <is>
-          <t>Postdoctoral Researcher in Finance (m/f/d)</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -46505,7 +46565,7 @@
       </c>
       <c r="H101" s="13" t="inlineStr">
         <is>
-          <t>Tenure-track Microeconomics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -46557,7 +46617,7 @@
       </c>
       <c r="H102" s="13" t="inlineStr">
         <is>
-          <t>Tenure-Track Macroeconomics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -46609,7 +46669,7 @@
       </c>
       <c r="H103" s="13" t="inlineStr">
         <is>
-          <t>Assistant Professor in Economics - Macroeconomics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -46666,7 +46726,7 @@
       </c>
       <c r="H104" s="13" t="inlineStr">
         <is>
-          <t>Lecturer (Assistant Professor)/Senior Lecturer/Associate Professor</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -46723,7 +46783,7 @@
       </c>
       <c r="H105" s="13" t="inlineStr">
         <is>
-          <t>Assistant Professor (W1) in Financial Economics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -46780,7 +46840,7 @@
       </c>
       <c r="H106" s="13" t="inlineStr">
         <is>
-          <t>Tenure-track position in applied economics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -46837,7 +46897,7 @@
       </c>
       <c r="H107" s="13" t="inlineStr">
         <is>
-          <t>Assistant / Associate / Full Professor</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -46894,7 +46954,7 @@
       </c>
       <c r="H108" s="13" t="inlineStr">
         <is>
-          <t>Faculty Positions at Department of Economics, Ashoka University (Open Rank)</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -46951,7 +47011,7 @@
       </c>
       <c r="H109" s="13" t="inlineStr">
         <is>
-          <t>Faculty Positions in Economics, AI &amp; Data Analytics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -47003,7 +47063,7 @@
       </c>
       <c r="H110" s="13" t="inlineStr">
         <is>
-          <t>Chair Professor/Professor/Associate Professor/Assistant Professor (Economics)</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -47060,7 +47120,7 @@
       </c>
       <c r="H111" s="13" t="inlineStr">
         <is>
-          <t>Assistant/Associate Professor level in Econometrics / Data Analytics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -47117,7 +47177,7 @@
       </c>
       <c r="H112" s="13" t="inlineStr">
         <is>
-          <t>Tenure track faculty position</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -47164,7 +47224,7 @@
       </c>
       <c r="H113" s="13" t="inlineStr">
         <is>
-          <t>Faculty Positions in Economics, Indian Institute of Management Bangalore</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -47221,7 +47281,7 @@
       </c>
       <c r="H114" s="13" t="inlineStr">
         <is>
-          <t>Economics Professor at Nova School of Business and Economics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -47278,7 +47338,7 @@
       </c>
       <c r="H115" s="13" t="inlineStr">
         <is>
-          <t>Tenure-Track Professor/Associate Professor/Assistant Professor (several posts)</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -47335,7 +47395,7 @@
       </c>
       <c r="H116" s="13" t="inlineStr">
         <is>
-          <t>Department of Economics (Tenure Track Position)</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -47382,7 +47442,7 @@
       </c>
       <c r="H117" s="13" t="inlineStr">
         <is>
-          <t>Assistant Professor of Economics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -47434,7 +47494,7 @@
       </c>
       <c r="H118" s="13" t="inlineStr">
         <is>
-          <t>Faculty of Economics at Plaksha University, India</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -47449,7 +47509,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -47481,7 +47541,7 @@
       </c>
       <c r="H119" s="13" t="inlineStr">
         <is>
-          <t>Assistant Professor - Economics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -47533,7 +47593,7 @@
       </c>
       <c r="H120" s="13" t="inlineStr">
         <is>
-          <t>Full Professor (chair) in Climate and Environmental Economics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -47558,7 +47618,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -47590,7 +47650,7 @@
       </c>
       <c r="H121" s="13" t="inlineStr">
         <is>
-          <t>Assistant/Associate/Full Professor, Dept. of Applied Economics, HEC Montréal</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -47647,7 +47707,7 @@
       </c>
       <c r="H122" s="13" t="inlineStr">
         <is>
-          <t>Assistant/Associate/Full Professor - Economics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -47699,7 +47759,7 @@
       </c>
       <c r="H123" s="13" t="inlineStr">
         <is>
-          <t>Lecturer/Senior Lecturer in Economics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -47751,7 +47811,7 @@
       </c>
       <c r="H124" s="13" t="inlineStr">
         <is>
-          <t>Assistant Professor / Associate Professor / Professor /</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -47803,7 +47863,7 @@
       </c>
       <c r="H125" s="13" t="inlineStr">
         <is>
-          <t>Two Assistants Professors Positions in Economics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -47855,7 +47915,7 @@
       </c>
       <c r="H126" s="13" t="inlineStr">
         <is>
-          <t>Faculty Positions in Finance</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -47907,7 +47967,7 @@
       </c>
       <c r="H127" s="13" t="inlineStr">
         <is>
-          <t>Assistant/Associate Professor of Economics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -47959,7 +48019,7 @@
       </c>
       <c r="H128" s="13" t="inlineStr">
         <is>
-          <t>Tenure-Track Faculty Position in Economics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -48016,7 +48076,7 @@
       </c>
       <c r="H129" s="13" t="inlineStr">
         <is>
-          <t>Open-rank Tenure-Track position in Economics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -48068,7 +48128,7 @@
       </c>
       <c r="H130" s="13" t="inlineStr">
         <is>
-          <t>Associate Professor (tenured)/Professor</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -48115,12 +48175,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="H131" s="13" t="inlineStr">
         <is>
-          <t>Assistant Professor/Associate Professor (tenure-track)</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -48177,7 +48237,7 @@
       </c>
       <c r="H132" s="13" t="inlineStr">
         <is>
-          <t>Senior Lecturer/Lecturer, Society Hub, HKUST(GZ)</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -48229,7 +48289,7 @@
       </c>
       <c r="H133" s="13" t="inlineStr">
         <is>
-          <t>Assistant/Associate Professor</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -48281,12 +48341,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="H134" s="13" t="inlineStr">
         <is>
-          <t>Assistant Professor of Economics - Any Field</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -48338,7 +48398,7 @@
       </c>
       <c r="H135" s="13" t="inlineStr">
         <is>
-          <t>Associate Professor/Professor</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -48390,7 +48450,7 @@
       </c>
       <c r="H136" s="13" t="inlineStr">
         <is>
-          <t>Assistant Professor and Postdoc positions at Universidad Complutense de Madrid</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -48437,12 +48497,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="H137" s="13" t="inlineStr">
         <is>
-          <t>Two Assistant Professor Positions in the Department of Decision Sciences</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -48489,12 +48549,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="H138" s="13" t="inlineStr">
         <is>
-          <t>Open Rank in Health Economics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -48541,12 +48601,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="H139" s="13" t="inlineStr">
         <is>
-          <t>Open Rank in Labor and Public Economics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -48598,7 +48658,7 @@
       </c>
       <c r="H140" s="13" t="inlineStr">
         <is>
-          <t>Tenure-track faculty in Finance, UNSW Business School</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -48655,7 +48715,7 @@
       </c>
       <c r="H141" s="13" t="inlineStr">
         <is>
-          <t>Tenure-Track Assistant Professor in Economics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -48712,7 +48772,7 @@
       </c>
       <c r="H142" s="13" t="inlineStr">
         <is>
-          <t>Lab Manager in Experimental Economics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -48769,7 +48829,7 @@
       </c>
       <c r="H143" s="13" t="inlineStr">
         <is>
-          <t>Associate Professor/Professor of Economics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -48826,7 +48886,7 @@
       </c>
       <c r="H144" s="13" t="inlineStr">
         <is>
-          <t>Stephen J.R. Smith Chair in Economics Policy</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -48883,7 +48943,7 @@
       </c>
       <c r="H145" s="13" t="inlineStr">
         <is>
-          <t>Assistant, Associate, or Full Professor Rank, Applied Microeconomics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -48935,7 +48995,7 @@
       </c>
       <c r="H146" s="13" t="inlineStr">
         <is>
-          <t>Assistant, Associate, or Full Professor Rank, Applied Microeconomics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -48982,12 +49042,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2027-03-01</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="H147" s="13" t="inlineStr">
         <is>
-          <t>Assistant Professor of Economics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -49039,7 +49099,7 @@
       </c>
       <c r="H148" s="13" t="inlineStr">
         <is>
-          <t>College of Economics at Shenzhen University</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -49091,7 +49151,7 @@
       </c>
       <c r="H149" s="13" t="inlineStr">
         <is>
-          <t>Assistant/Associate Professor of Finance</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -49143,7 +49203,7 @@
       </c>
       <c r="H150" s="13" t="inlineStr">
         <is>
-          <t>Assistant/Associate Professor of Economics (Macroeconomics)</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -49200,7 +49260,7 @@
       </c>
       <c r="H151" s="13" t="inlineStr">
         <is>
-          <t>Finance and Business Economics Area – CIBC Chair in Financial Markets</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -49252,12 +49312,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2027-04-30</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="H152" s="13" t="inlineStr">
         <is>
-          <t>Assistant Professor, Teaching Stream - Macroeconomics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -49314,7 +49374,7 @@
       </c>
       <c r="H153" s="13" t="inlineStr">
         <is>
-          <t>Economics Faculty Positions at the Thapar School of Liberal Arts and Sciences</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -49371,7 +49431,7 @@
       </c>
       <c r="H154" s="13" t="inlineStr">
         <is>
-          <t>Associate/Full Professor of Agricultural Economics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -49418,7 +49478,7 @@
       </c>
       <c r="H155" s="13" t="inlineStr">
         <is>
-          <t>Assistant/Associate Professor of Economics (Microeconomics)</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -49470,7 +49530,7 @@
       </c>
       <c r="H156" s="13" t="inlineStr">
         <is>
-          <t>Assistant/Associate/Full Professor of Economics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -49527,7 +49587,7 @@
       </c>
       <c r="H157" s="13" t="inlineStr">
         <is>
-          <t>Postdoctoral Position Available in Environmental Economics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -49552,7 +49612,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Postdoc</t>
+          <t>Faculty</t>
         </is>
       </c>
     </row>
@@ -49579,12 +49639,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="H158" s="13" t="inlineStr">
         <is>
-          <t>Postdoctoral Fellowship in Economics (WORK4ALL-MH Project)</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -49641,7 +49701,7 @@
       </c>
       <c r="H159" s="13" t="inlineStr">
         <is>
-          <t>Postdoctoral Fellow in Business and Administration</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -49698,7 +49758,7 @@
       </c>
       <c r="H160" s="13" t="inlineStr">
         <is>
-          <t>Postdoctoral Fellowship in Philosophy, Politics and Economics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -49755,7 +49815,7 @@
       </c>
       <c r="H161" s="13" t="inlineStr">
         <is>
-          <t>Post-Doctoral Position in Macroeconomics, Public Economics, Household Finance</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -49802,7 +49862,7 @@
       </c>
       <c r="H162" s="13" t="inlineStr">
         <is>
-          <t>Postdoctoral Fellow Positions in Platform Economics and Market Design, CUHK(SZ)</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -49859,7 +49919,7 @@
       </c>
       <c r="H163" s="13" t="inlineStr">
         <is>
-          <t>Research Associate (Postdoctoral Scholar) in Wealth Inequality</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -49911,7 +49971,7 @@
       </c>
       <c r="H164" s="13" t="inlineStr">
         <is>
-          <t>Research Associate (Postdoctoral Scholar) in Economic Inequality</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -49963,7 +50023,7 @@
       </c>
       <c r="H165" s="13" t="inlineStr">
         <is>
-          <t>Postdoc in AI agents and human-AI interactions in financial systems</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -50020,7 +50080,7 @@
       </c>
       <c r="H166" s="13" t="inlineStr">
         <is>
-          <t>Postdoctoral Fellow in Economics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -50077,7 +50137,7 @@
       </c>
       <c r="H167" s="13" t="inlineStr">
         <is>
-          <t>Research Fellow</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -50129,7 +50189,7 @@
       </c>
       <c r="H168" s="13" t="inlineStr">
         <is>
-          <t>Postdoctoral Fellow</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -50181,7 +50241,7 @@
       </c>
       <c r="H169" s="13" t="inlineStr">
         <is>
-          <t>Senior Research Fellows/Postdocs (m/f/d) in Management / Economics of Innovation</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -50228,7 +50288,7 @@
       </c>
       <c r="H170" s="13" t="inlineStr">
         <is>
-          <t>Postdoctoral Fellow in Financial Decision-Making</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -50280,7 +50340,7 @@
       </c>
       <c r="H171" s="13" t="inlineStr">
         <is>
-          <t>Two postdoctoral researcher positions (E13 TV-L, full-time)</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -50337,7 +50397,7 @@
       </c>
       <c r="H172" s="13" t="inlineStr">
         <is>
-          <t>Postdoctoral Researcher in Finance, Asset Pricing</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -50389,7 +50449,7 @@
       </c>
       <c r="H173" s="13" t="inlineStr">
         <is>
-          <t>Research Associate in Labor Economics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -50446,7 +50506,7 @@
       </c>
       <c r="H174" s="13" t="inlineStr">
         <is>
-          <t>Postdoctoral researcher at Nova School of Business and Economics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -50503,7 +50563,7 @@
       </c>
       <c r="H175" s="13" t="inlineStr">
         <is>
-          <t>Postdoctoral Researcher in Innovation Economics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -50560,7 +50620,7 @@
       </c>
       <c r="H176" s="13" t="inlineStr">
         <is>
-          <t>Postdoctoral Researcher in Political Economy</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -50612,7 +50672,7 @@
       </c>
       <c r="H177" s="13" t="inlineStr">
         <is>
-          <t>Research Fellowships CSEF - DISES</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -50664,12 +50724,12 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="H178" s="13" t="inlineStr">
         <is>
-          <t>Postdoctoral Associate, Charter Schools</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -50721,12 +50781,12 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="H179" s="13" t="inlineStr">
         <is>
-          <t>Postdoctoral Associate, AI in Education</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -50783,7 +50843,7 @@
       </c>
       <c r="H180" s="13" t="inlineStr">
         <is>
-          <t>Postdoctoral Researcher in Economics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -50840,7 +50900,7 @@
       </c>
       <c r="H181" s="13" t="inlineStr">
         <is>
-          <t>Postdoctoral Fellow in Global Entrepreneurship</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -50897,7 +50957,7 @@
       </c>
       <c r="H182" s="13" t="inlineStr">
         <is>
-          <t>Post-Doctoral Fellowships in Economics of Education</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -50954,7 +51014,7 @@
       </c>
       <c r="H183" s="13" t="inlineStr">
         <is>
-          <t>Post-Doc in Energy Economics, the Climate and the Green Energy Transition</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -51011,7 +51071,7 @@
       </c>
       <c r="H184" s="13" t="inlineStr">
         <is>
-          <t>Post-Doctoral Fellowship in Econometrics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -51068,7 +51128,7 @@
       </c>
       <c r="H185" s="13" t="inlineStr">
         <is>
-          <t>Post-Doc in the Automation and Labor Market in the Global Economy</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -51125,7 +51185,7 @@
       </c>
       <c r="H186" s="13" t="inlineStr">
         <is>
-          <t>Post-Doctoral Fellowship in Microeconomic Theory/Decision Theory</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -51182,7 +51242,7 @@
       </c>
       <c r="H187" s="13" t="inlineStr">
         <is>
-          <t>Postdoctoral Researcher (3 Years) – Transport / Urban Economics / Data Science</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -51239,7 +51299,7 @@
       </c>
       <c r="H188" s="13" t="inlineStr">
         <is>
-          <t>International Research Fellow</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -51291,7 +51351,7 @@
       </c>
       <c r="H189" s="13" t="inlineStr">
         <is>
-          <t>Postdoctoral scholarship (3 years) in Economics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -51343,7 +51403,7 @@
       </c>
       <c r="H190" s="13" t="inlineStr">
         <is>
-          <t>Postdoctoral Fellowships (x2): Economic Growth</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -51400,7 +51460,7 @@
       </c>
       <c r="H191" s="13" t="inlineStr">
         <is>
-          <t>Postdoctoral Researchers in Economics and Data Science (2 positions)</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -51425,7 +51485,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Postdoc</t>
+          <t>Faculty</t>
         </is>
       </c>
     </row>
@@ -51457,7 +51517,7 @@
       </c>
       <c r="H192" s="13" t="inlineStr">
         <is>
-          <t>Postdoctoral Research Fellowship in Economics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -51499,7 +51559,7 @@
       </c>
       <c r="H193" s="13" t="inlineStr">
         <is>
-          <t>Postdoctoral position - Causal inference in electronic health record data</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -51541,7 +51601,7 @@
       </c>
       <c r="H194" s="13" t="inlineStr">
         <is>
-          <t>Postdoctoral position - Causal inference in electronic health record data</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -51593,7 +51653,7 @@
       </c>
       <c r="H195" s="13" t="inlineStr">
         <is>
-          <t>Postdoctoral Research Fellow in Industrial Organization</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -51650,7 +51710,7 @@
       </c>
       <c r="H196" s="13" t="inlineStr">
         <is>
-          <t>Postdoctoral Research Associate</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
@@ -51697,7 +51757,7 @@
       </c>
       <c r="H197" s="13" t="inlineStr">
         <is>
-          <t>3-year fixed-term International Research Fellows</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -51749,12 +51809,12 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2027-04-07</t>
         </is>
       </c>
       <c r="H198" s="13" t="inlineStr">
         <is>
-          <t>Bank of Finland Research Unit Visiting Scholars Programme</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
@@ -51786,12 +51846,12 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="H199" s="13" t="inlineStr">
         <is>
-          <t>Community Development Research Fellow</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -51838,12 +51898,12 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="H200" s="13" t="inlineStr">
         <is>
-          <t>Research Fellow</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -51900,7 +51960,7 @@
       </c>
       <c r="H201" s="13" t="inlineStr">
         <is>
-          <t>Research Economist</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -51957,7 +52017,7 @@
       </c>
       <c r="H202" s="13" t="inlineStr">
         <is>
-          <t>Research Economist</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -52014,7 +52074,7 @@
       </c>
       <c r="H203" s="13" t="inlineStr">
         <is>
-          <t>Research Economist</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -52071,7 +52131,7 @@
       </c>
       <c r="H204" s="13" t="inlineStr">
         <is>
-          <t>Research Analyst (Economist)</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -52128,7 +52188,7 @@
       </c>
       <c r="H205" s="13" t="inlineStr">
         <is>
-          <t>Senior Associate (m/f/d) - Competition Economics Consultancy</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -52185,7 +52245,7 @@
       </c>
       <c r="H206" s="13" t="inlineStr">
         <is>
-          <t>Junior Economists/ Economists</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -52242,7 +52302,7 @@
       </c>
       <c r="H207" s="13" t="inlineStr">
         <is>
-          <t>Senior Associate (North America)</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -52299,7 +52359,7 @@
       </c>
       <c r="H208" s="13" t="inlineStr">
         <is>
-          <t>Senior Associate/Antitrust &amp; Competition Economics (Europe)</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -52356,7 +52416,7 @@
       </c>
       <c r="H209" s="13" t="inlineStr">
         <is>
-          <t>PhD Internship, Economics and Finance</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -52413,7 +52473,7 @@
       </c>
       <c r="H210" s="13" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of Dallas</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -52465,7 +52525,7 @@
       </c>
       <c r="H211" s="13" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of Dallas</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -52517,7 +52577,7 @@
       </c>
       <c r="H212" s="13" t="inlineStr">
         <is>
-          <t>Research Economist</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
@@ -52569,7 +52629,7 @@
       </c>
       <c r="H213" s="13" t="inlineStr">
         <is>
-          <t>Economists or Research Advisors</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -52626,7 +52686,7 @@
       </c>
       <c r="H214" s="13" t="inlineStr">
         <is>
-          <t>Economist</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
@@ -52673,7 +52733,7 @@
       </c>
       <c r="H215" s="13" t="inlineStr">
         <is>
-          <t>[KIPF] Research FeIIow</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -52730,7 +52790,7 @@
       </c>
       <c r="H216" s="13" t="inlineStr">
         <is>
-          <t>Senior Economist or Economic Advisor and Economist</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -52787,7 +52847,7 @@
       </c>
       <c r="H217" s="13" t="inlineStr">
         <is>
-          <t>Researcher/Senior Researcher</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -52844,7 +52904,7 @@
       </c>
       <c r="H218" s="13" t="inlineStr">
         <is>
-          <t>Economist</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
@@ -52891,12 +52951,12 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="H219" s="13" t="inlineStr">
         <is>
-          <t>Economist/Senior Economist/Economic Policy Advisor</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -52948,7 +53008,7 @@
       </c>
       <c r="H220" s="13" t="inlineStr">
         <is>
-          <t>Internship / Stagiaire IPP</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
@@ -53000,7 +53060,7 @@
       </c>
       <c r="H221" s="13" t="inlineStr">
         <is>
-          <t>Candidature spontanée / unsolicited application</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
@@ -53052,7 +53112,7 @@
       </c>
       <c r="H222" s="13" t="inlineStr">
         <is>
-          <t>Economist</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
@@ -53099,7 +53159,7 @@
       </c>
       <c r="H223" s="13" t="inlineStr">
         <is>
-          <t>Junior Economist</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -53146,12 +53206,12 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="H224" s="13" t="inlineStr">
         <is>
-          <t>Senior Economist/Economic Policy Advisor/Senior Economic Policy Advisor</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -53198,12 +53258,12 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>2027-04-30</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="H225" s="13" t="inlineStr">
         <is>
-          <t>PhD Researcher (2026-2027 PhD Job Market)</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -53693,23 +53753,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="11" t="inlineStr">
@@ -53786,27 +53831,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Central University of Finance and Economics</t>
+          <t>Dongbei University of Finance &amp; Economics</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>School of Economics</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2019-11-20</t>
+          <t>Dongbei University Of Finance And Economics</t>
         </is>
       </c>
       <c r="H2" s="13" t="inlineStr">
         <is>
-          <t>School of Economics</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>CV; Job Market Paper; Letters of Reference</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -53816,7 +53851,7 @@
       </c>
       <c r="K2" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=BBEFCB01CDC38CBD</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=9058523321C2911A</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -53833,17 +53868,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dongbei University of Finance &amp; Economics</t>
+          <t>Anhui University of Finance and Economics</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Dongbei University Of Finance And Economics</t>
+          <t>School of Economics</t>
         </is>
       </c>
       <c r="H3" s="13" t="inlineStr">
         <is>
-          <t>Dongbei University Of Finance And Economics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -53853,12 +53888,12 @@
       </c>
       <c r="K3" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=9058523321C2911A</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=D43F9930BDD332A2</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -53870,17 +53905,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jilin University</t>
+          <t>Ant Group Research</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Business School</t>
+          <t>Full-time Postdoctoral Researcher</t>
         </is>
       </c>
       <c r="H4" s="13" t="inlineStr">
         <is>
-          <t>Business School</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -53890,12 +53925,12 @@
       </c>
       <c r="K4" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=A4E054BFC7078E2F</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=BE0705D307C4EA24</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -53907,17 +53942,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Anhui University of Finance and Economics</t>
+          <t>Beijing Institute of Technology</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>School of Economics</t>
+          <t>School of Management and Economics</t>
         </is>
       </c>
       <c r="H5" s="13" t="inlineStr">
         <is>
-          <t>School of Economics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -53927,12 +53962,12 @@
       </c>
       <c r="K5" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=D43F9930BDD332A2</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=1D0A7E0E5861506A</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -53944,17 +53979,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ant Group Research</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Full-time Postdoctoral Researcher</t>
+          <t>Beijing Jiaotong University School of Economics and Management</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Rolling</t>
         </is>
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>Full-time Postdoctoral Researcher</t>
+          <t>Listing</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>CV; Job Market Paper; Letters of Reference</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -53964,7 +54004,7 @@
       </c>
       <c r="K6" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=BE0705D307C4EA24</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=223BE806CD01DB59</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -53981,22 +54021,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Beihang University</t>
+          <t>Beijing Normal University</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>School of Economics and Management</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2023-11-30</t>
+          <t>BAY AREA INTERNATIONAL BUSINESS SCHOOL</t>
         </is>
       </c>
       <c r="H7" s="13" t="inlineStr">
         <is>
-          <t>School of Economics and Management</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -54006,7 +54041,7 @@
       </c>
       <c r="K7" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=2A622CF706A4EC66</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=4AC7F281ECBD2BA4</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -54023,17 +54058,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Beijing Institute of Technology</t>
+          <t>Donghua University</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>School of Management and Economics</t>
+          <t>Glorious Sun School of Business and Management</t>
         </is>
       </c>
       <c r="H8" s="13" t="inlineStr">
         <is>
-          <t>School of Management and Economics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -54043,7 +54078,7 @@
       </c>
       <c r="K8" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=1D0A7E0E5861506A</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=1CE68DDB85B84365</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -54060,22 +54095,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Beijing Jiaotong University School of Economics and Management</t>
+          <t>Fudan University</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>School of Economics</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rolling</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="H9" s="13" t="inlineStr">
         <is>
-          <t>Beijing Jiaotong University School of Economics and Management</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>CV; Job Market Paper; Letters of Reference</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -54085,7 +54120,7 @@
       </c>
       <c r="K9" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=223BE806CD01DB59</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=E968D280DD59D564</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -54102,17 +54137,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Beijing Normal University</t>
+          <t>Fudan University</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>BAY AREA INTERNATIONAL BUSINESS SCHOOL</t>
+          <t>School of Management</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Rolling</t>
         </is>
       </c>
       <c r="H10" s="13" t="inlineStr">
         <is>
-          <t>BAY AREA INTERNATIONAL BUSINESS SCHOOL</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -54122,12 +54162,12 @@
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=4AC7F281ECBD2BA4</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=E153FEE8CC8E11B5</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -54139,17 +54179,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Capital University of Economics and Business</t>
+          <t>Harbin Institute of Technology</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>International School of Economics and Management</t>
+          <t>School of Management</t>
         </is>
       </c>
       <c r="H11" s="13" t="inlineStr">
         <is>
-          <t>International School of Economics and Management</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -54159,7 +54199,7 @@
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=230A8F8CAE8FB702</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=3ED8A58471D2F80B</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -54176,22 +54216,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dongbei University of Finance &amp; Economics</t>
+          <t>Huazhong University of Science and Technology</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Institute for Advanced Economic Research</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2024-12-01</t>
+          <t>School of Economics, Huazhong University of Science &amp; Technology</t>
         </is>
       </c>
       <c r="H12" s="13" t="inlineStr">
         <is>
-          <t>Institute for Advanced Economic Research</t>
+          <t>Listing</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>CV; Job Market Paper; Letters of Reference</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -54201,12 +54241,12 @@
       </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=416DCA32DD657A3E</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=A380FA8882023C78</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -54218,17 +54258,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Donghua University</t>
+          <t>Hunan University</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Glorious Sun School of Business and Management</t>
+          <t>School of Economics and Trade</t>
         </is>
       </c>
       <c r="H13" s="13" t="inlineStr">
         <is>
-          <t>Glorious Sun School of Business and Management</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -54238,12 +54278,12 @@
       </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=1CE68DDB85B84365</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=38CE3CA2770AB83B</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -54255,22 +54295,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>East China Normal University</t>
+          <t>Lanzhou University of Finance and Economics</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>School of Economics and Management</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2025-11-28</t>
+          <t>the Office of Personnel</t>
         </is>
       </c>
       <c r="H14" s="13" t="inlineStr">
         <is>
-          <t>School of Economics and Management</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -54280,7 +54315,7 @@
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=02D0B642A4713897</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=003923B6EFE42FFF</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -54297,22 +54332,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Fudan University</t>
+          <t>Nanjing Agricultural University</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>School of Economics</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-11-01</t>
+          <t>College of Finance</t>
         </is>
       </c>
       <c r="H15" s="13" t="inlineStr">
         <is>
-          <t>School of Economics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -54322,7 +54352,7 @@
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=E968D280DD59D564</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=41CE1E8D1AE20F34</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -54339,22 +54369,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Fudan University</t>
+          <t>Nanjing University</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>School of Management</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Rolling</t>
+          <t>Business School</t>
         </is>
       </c>
       <c r="H16" s="13" t="inlineStr">
         <is>
-          <t>School of Management</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -54364,7 +54389,7 @@
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=E153FEE8CC8E11B5</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=5EE87D5DE6734D4D</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -54381,22 +54406,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Fudan University</t>
+          <t>Peking University</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>International School of Finance</t>
+          <t>Guanghua School of Management</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>Rolling</t>
         </is>
       </c>
       <c r="H17" s="13" t="inlineStr">
         <is>
-          <t>International School of Finance</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -54406,7 +54431,7 @@
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=1EB0900D191FE938</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=B2D1A3FBC0575542</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -54423,17 +54448,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Harbin Institute of Technology</t>
+          <t>Peking University</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>School of Management</t>
+          <t>Peking University HSBC Business School</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="H18" s="13" t="inlineStr">
         <is>
-          <t>School of Management</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -54443,7 +54473,7 @@
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=3ED8A58471D2F80B</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=6AA44C52147BF1AA</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -54460,22 +54490,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Huazhong University of Science and Technology</t>
+          <t>Renmin University of China</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>School of Economics, Huazhong University of Science &amp; Technology</t>
+          <t>School of Finance, Renmin University of China</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="H19" s="13" t="inlineStr">
         <is>
-          <t>School of Economics, Huazhong University of Science &amp; Technology</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>CV; Job Market Paper; Letters of Reference</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -54485,7 +54515,7 @@
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=A380FA8882023C78</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=A2C98A6CF51DA6B8</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -54502,17 +54532,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Hunan University</t>
+          <t>Shanghai Institute for Mathematics and Interdisciplinary Sciences</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>School of Economics and Trade</t>
+          <t>The Shanghai Institute for Mathematics and Interdisciplinary Sciences</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Rolling</t>
         </is>
       </c>
       <c r="H20" s="13" t="inlineStr">
         <is>
-          <t>School of Economics and Trade</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -54522,7 +54557,7 @@
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=38CE3CA2770AB83B</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=D6296C379B46AFF9</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -54539,22 +54574,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jinan University</t>
+          <t>Shanghai Jiao Tong University</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>School of Economics(SOE)</t>
+          <t>Antai College of Economics and Management</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2023-11-30</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="H21" s="13" t="inlineStr">
         <is>
-          <t>School of Economics(SOE)</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -54564,7 +54599,7 @@
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=071E9B3AC5A0F760</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=A718B6651C5FE241</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -54581,17 +54616,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lanzhou University of Finance and Economics</t>
+          <t>Shanghai University of Finance and Economics</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>the Office of Personnel</t>
+          <t>School of Economics</t>
         </is>
       </c>
       <c r="H22" s="13" t="inlineStr">
         <is>
-          <t>the Office of Personnel</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -54601,7 +54636,7 @@
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=003923B6EFE42FFF</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=3E6981392FF08E75</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -54618,17 +54653,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Nanjing Agricultural University</t>
+          <t>Sun Yat-sen University</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>College of Finance</t>
+          <t>Lingnan College</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Rolling</t>
         </is>
       </c>
       <c r="H23" s="13" t="inlineStr">
         <is>
-          <t>College of Finance</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -54638,12 +54678,12 @@
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=41CE1E8D1AE20F34</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=73CF283104D9C7BB</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -54655,17 +54695,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Nanjing University</t>
+          <t>Tsinghua University</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Business School</t>
+          <t>School of Economics and Management</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="H24" s="13" t="inlineStr">
         <is>
-          <t>Business School</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -54675,7 +54720,7 @@
       </c>
       <c r="K24" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=5EE87D5DE6734D4D</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=EB34146E1220A115</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -54692,22 +54737,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Nankai University</t>
+          <t>Tsinghua University</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>School of Economics</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2025-12-07</t>
+          <t>Center for International Finance and Economics Research</t>
         </is>
       </c>
       <c r="H25" s="13" t="inlineStr">
         <is>
-          <t>School of Economics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -54717,12 +54757,12 @@
       </c>
       <c r="K25" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=FDC08442010B7BC2</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=6A1E66715A3A82D9</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -54734,17 +54774,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Nankai University</t>
+          <t>University of Electronic Science and Technology of China</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>School of Finance</t>
+          <t>School of Management and Economics</t>
         </is>
       </c>
       <c r="H26" s="13" t="inlineStr">
         <is>
-          <t>School of Finance</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -54754,12 +54794,12 @@
       </c>
       <c r="K26" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=96728BEC2B0A48B6</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=390B333672086D05</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -54771,22 +54811,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Peking University</t>
+          <t>University of Science and Technology of China</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Guanghua School of Management</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Rolling</t>
+          <t>School of Management</t>
         </is>
       </c>
       <c r="H27" s="13" t="inlineStr">
         <is>
-          <t>Guanghua School of Management</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -54796,7 +54831,7 @@
       </c>
       <c r="K27" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=B2D1A3FBC0575542</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=6CAF00207D46BD36</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -54813,22 +54848,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Peking University</t>
+          <t>University of Science and Technology of China</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Peking University HSBC Business School</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-12-08</t>
+          <t>Institute of International Finance</t>
         </is>
       </c>
       <c r="H28" s="13" t="inlineStr">
         <is>
-          <t>Peking University HSBC Business School</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -54838,12 +54868,12 @@
       </c>
       <c r="K28" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=6AA44C52147BF1AA</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=612A2FEECB1FB3D7</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -54855,27 +54885,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Renmin University of China</t>
+          <t>Xi%u2019an Jiaotong University</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>School of Economics</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2025-12-02</t>
+          <t>School of Economics and Finance</t>
         </is>
       </c>
       <c r="H29" s="13" t="inlineStr">
         <is>
-          <t>School of Economics</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>CV; Job Market Paper; Letters of Reference</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -54885,7 +54905,7 @@
       </c>
       <c r="K29" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=D7AB329AF0E6B516</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=C3A72C51D391769E</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -54902,22 +54922,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Renmin University of China</t>
+          <t>Xi%u2019an Jiaotong-Liverpool University</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>School of Finance, Renmin University of China</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-12-01</t>
+          <t>International Business School Suzhou (IBSS), Department of Economics</t>
         </is>
       </c>
       <c r="H30" s="13" t="inlineStr">
         <is>
-          <t>School of Finance, Renmin University of China</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -54927,7 +54942,7 @@
       </c>
       <c r="K30" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=A2C98A6CF51DA6B8</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=038CBF83FD61166B</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -54944,22 +54959,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Shanghai Institute for Mathematics and Interdisciplinary Sciences</t>
+          <t>Zhejiang University</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>The Shanghai Institute for Mathematics and Interdisciplinary Sciences</t>
+          <t>School of Economics</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>Rolling</t>
         </is>
       </c>
       <c r="H31" s="13" t="inlineStr">
         <is>
-          <t>The Shanghai Institute for Mathematics and Interdisciplinary Sciences</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -54969,7 +54984,7 @@
       </c>
       <c r="K31" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=D6296C379B46AFF9</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=7D928B7B1C35099A</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -54986,22 +55001,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Shanghai Jiao Tong University</t>
+          <t>Zhejiang University</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Antai College of Economics and Management</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-11-15</t>
+          <t>International Business School</t>
         </is>
       </c>
       <c r="H32" s="13" t="inlineStr">
         <is>
-          <t>Antai College of Economics and Management</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -55011,12 +55021,12 @@
       </c>
       <c r="K32" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=A718B6651C5FE241</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=AB6EF80CCC4E40B3</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -55028,17 +55038,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Shanghai University of Finance and Economics</t>
+          <t>Zhongnan Unviersity of Economics and Law</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>School of Economics</t>
+          <t>School of Finance</t>
         </is>
       </c>
       <c r="H33" s="13" t="inlineStr">
         <is>
-          <t>School of Economics</t>
+          <t>Listing</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -55048,758 +55058,10 @@
       </c>
       <c r="K33" s="13" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=3E6981392FF08E75</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=2FC3B168FE2DBD23</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
-        <is>
-          <t>Faculty</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Shanghai University of Finance Economics School</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>School of Digital Economy</t>
-        </is>
-      </c>
-      <c r="H34" s="13" t="inlineStr">
-        <is>
-          <t>School of Digital Economy</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>CICE</t>
-        </is>
-      </c>
-      <c r="K34" s="13" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=7E509CEAE1E65959</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>Faculty</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Sichuan University</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>The School of Economics of Sichuan University</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
-      <c r="H35" s="13" t="inlineStr">
-        <is>
-          <t>The School of Economics of Sichuan University</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>CICE</t>
-        </is>
-      </c>
-      <c r="K35" s="13" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=4D01E5935B5738A3</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>Faculty</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Southern University of Science and Technology</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2023-12-10</t>
-        </is>
-      </c>
-      <c r="H36" s="13" t="inlineStr">
-        <is>
-          <t>Southern University of Science and Technology</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>CICE</t>
-        </is>
-      </c>
-      <c r="K36" s="13" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=3EF86BA9413BD79E</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>Faculty</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Southwestern University of Finance and Economics</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>School of Economics</t>
-        </is>
-      </c>
-      <c r="H37" s="13" t="inlineStr">
-        <is>
-          <t>School of Economics</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>CICE</t>
-        </is>
-      </c>
-      <c r="K37" s="13" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=8F2A4E7B41A62BEC</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>Faculty</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Southwestern University of Finance&amp;;Economics</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Research Institute of Economics and Management</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2023-12-01</t>
-        </is>
-      </c>
-      <c r="H38" s="13" t="inlineStr">
-        <is>
-          <t>Research Institute of Economics and Management</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>CV; Job Market Paper; Letters of Reference</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>CICE</t>
-        </is>
-      </c>
-      <c r="K38" s="13" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=DB9471D924F0FD44</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>Faculty</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Sun Yat-sen University</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Lingnan College</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2023-05-12</t>
-        </is>
-      </c>
-      <c r="H39" s="13" t="inlineStr">
-        <is>
-          <t>Lingnan College</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>CICE</t>
-        </is>
-      </c>
-      <c r="K39" s="13" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=73CF283104D9C7BB</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>Faculty</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>The Chinese University of Hong Kong</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Department of Economics</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="H40" s="13" t="inlineStr">
-        <is>
-          <t>Department of Economics</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>CICE</t>
-        </is>
-      </c>
-      <c r="K40" s="13" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=0204A4EECEEA66C1</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>Faculty</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Tianjin University</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Ma Yinchu School of Economics</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2023-11-15</t>
-        </is>
-      </c>
-      <c r="H41" s="13" t="inlineStr">
-        <is>
-          <t>Ma Yinchu School of Economics</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>CICE</t>
-        </is>
-      </c>
-      <c r="K41" s="13" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=3514AA8724F3F9F8</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>Faculty</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Tsinghua University</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>School of Economics and Management</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2026-11-30</t>
-        </is>
-      </c>
-      <c r="H42" s="13" t="inlineStr">
-        <is>
-          <t>School of Economics and Management</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>CICE</t>
-        </is>
-      </c>
-      <c r="K42" s="13" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=EB34146E1220A115</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>Faculty</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Tsinghua University</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Center for International Finance and Economics Research</t>
-        </is>
-      </c>
-      <c r="H43" s="13" t="inlineStr">
-        <is>
-          <t>Center for International Finance and Economics Research</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>CICE</t>
-        </is>
-      </c>
-      <c r="K43" s="13" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=6A1E66715A3A82D9</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>Faculty</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>University of Electronic Science and Technology of China</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>School of Management and Economics</t>
-        </is>
-      </c>
-      <c r="H44" s="13" t="inlineStr">
-        <is>
-          <t>School of Management and Economics</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>CICE</t>
-        </is>
-      </c>
-      <c r="K44" s="13" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=390B333672086D05</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>Faculty</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>University of Science and Technology of China</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>School of Management</t>
-        </is>
-      </c>
-      <c r="H45" s="13" t="inlineStr">
-        <is>
-          <t>School of Management</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>CICE</t>
-        </is>
-      </c>
-      <c r="K45" s="13" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=6CAF00207D46BD36</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>Faculty</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>University of Science and Technology of China</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Institute of International Finance</t>
-        </is>
-      </c>
-      <c r="H46" s="13" t="inlineStr">
-        <is>
-          <t>Institute of International Finance</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>CICE</t>
-        </is>
-      </c>
-      <c r="K46" s="13" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=612A2FEECB1FB3D7</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>Faculty</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Wuhan University</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>School of Economics and Management</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2023-11-30</t>
-        </is>
-      </c>
-      <c r="H47" s="13" t="inlineStr">
-        <is>
-          <t>School of Economics and Management</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>CICE</t>
-        </is>
-      </c>
-      <c r="K47" s="13" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=A2DDB669D0484F72</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>Faculty</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Xi%u2019an Jiaotong University</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>School of Economics and Finance</t>
-        </is>
-      </c>
-      <c r="H48" s="13" t="inlineStr">
-        <is>
-          <t>School of Economics and Finance</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>CICE</t>
-        </is>
-      </c>
-      <c r="K48" s="13" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=C3A72C51D391769E</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>Faculty</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Xi%u2019an Jiaotong-Liverpool University</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>International Business School Suzhou (IBSS), Department of Economics</t>
-        </is>
-      </c>
-      <c r="H49" s="13" t="inlineStr">
-        <is>
-          <t>International Business School Suzhou (IBSS), Department of Economics</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>CICE</t>
-        </is>
-      </c>
-      <c r="K49" s="13" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=038CBF83FD61166B</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>Faculty</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Zhejiang University</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>School of Economics</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="H50" s="13" t="inlineStr">
-        <is>
-          <t>School of Economics</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>CICE</t>
-        </is>
-      </c>
-      <c r="K50" s="13" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=7D928B7B1C35099A</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>Faculty</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Zhejiang University</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>International Business School</t>
-        </is>
-      </c>
-      <c r="H51" s="13" t="inlineStr">
-        <is>
-          <t>International Business School</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>CICE</t>
-        </is>
-      </c>
-      <c r="K51" s="13" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=AB6EF80CCC4E40B3</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>Faculty</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Zhongnan Unviersity of Economics and Law</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>School of Finance</t>
-        </is>
-      </c>
-      <c r="H52" s="13" t="inlineStr">
-        <is>
-          <t>School of Finance</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>CICE</t>
-        </is>
-      </c>
-      <c r="K52" s="13" t="inlineStr">
-        <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=2FC3B168FE2DBD23</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
         <is>
           <t>Faculty</t>
         </is>
@@ -55871,44 +55133,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId62"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId63"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K44" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K45" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K46" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H48" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K48" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H49" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K49" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H50" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K50" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H51" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K51" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H52" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K52" r:id="rId102"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
